--- a/web_ces/indicadores/SFE-VTMA_out.xlsx
+++ b/web_ces/indicadores/SFE-VTMA_out.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/web_ces/indicadores/SFE-VTMA_out.xlsx
+++ b/web_ces/indicadores/SFE-VTMA_out.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">fleiva</t>
+    <t xml:space="preserve">ysonder</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
